--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2365-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2365-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0C0D72F-3CBB-4420-A3B3-899729382842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C44F15B5-8475-4D1A-AA5E-5E9F32A93513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{A108ADDD-5CD7-41CA-B715-EFC69A80F4DC}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{43ADD331-DD00-4270-9935-2F9C5F704682}"/>
   </bookViews>
   <sheets>
     <sheet name="2365-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1532,21 +1532,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9A52BF-216F-408B-A40D-062B093336B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D22BDE-0E96-4995-BA7D-42E576A17187}">
   <dimension ref="A1:R79"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1604,7 +1604,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1700,7 +1700,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2025</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
         <v>2024</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2023</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>25</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>25</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>25</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2022</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>25</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>25</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>25</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>25</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2021</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>25</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
         <v>25</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>25</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
         <v>25</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>25</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>25</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>2020</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>25</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>25</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>25</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>25</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>2019</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
         <v>25</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
         <v>25</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>25</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
         <v>25</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="38">
         <v>2018</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="40">
         <v>2017</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="38">
         <v>2016</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="40">
         <v>2015</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="38">
         <v>2014</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="40">
         <v>2013</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="38">
         <v>2012</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="40">
         <v>2011</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="38">
         <v>2010</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="40">
         <v>2009</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="38">
         <v>2008</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="40">
         <v>2007</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="38">
         <v>2006</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="40">
         <v>2005</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="38">
         <v>2004</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="40">
         <v>2003</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="38">
         <v>2002</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="70" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="40">
         <v>2001</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="71" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="38">
         <v>2000</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="40">
         <v>1999</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="73" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="38">
         <v>1998</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="74" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="40">
         <v>1997</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="75" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="38">
         <v>1996</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="40">
         <v>1995</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="38">
         <v>1994</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="40">
         <v>1993</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
         <v>62</v>
       </c>
